--- a/artfynd/A 46548-2023 artfynd.xlsx
+++ b/artfynd/A 46548-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504975</v>
+        <v>118505057</v>
       </c>
       <c r="B3" t="n">
-        <v>97764</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562401</v>
+        <v>562450</v>
       </c>
       <c r="R3" t="n">
-        <v>6923859</v>
+        <v>6923797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118505057</v>
+        <v>118504966</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562450</v>
+        <v>562527</v>
       </c>
       <c r="R4" t="n">
-        <v>6923797</v>
+        <v>6923740</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504944</v>
+        <v>118504975</v>
       </c>
       <c r="B5" t="n">
-        <v>91436</v>
+        <v>97764</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,38 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562381</v>
+        <v>562401</v>
       </c>
       <c r="R5" t="n">
-        <v>6923819</v>
+        <v>6923859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504966</v>
+        <v>118504944</v>
       </c>
       <c r="B6" t="n">
-        <v>97867</v>
+        <v>91436</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,34 +1103,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562527</v>
+        <v>562381</v>
       </c>
       <c r="R6" t="n">
-        <v>6923740</v>
+        <v>6923819</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 46548-2023 artfynd.xlsx
+++ b/artfynd/A 46548-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504974</v>
+        <v>118505057</v>
       </c>
       <c r="B2" t="n">
-        <v>97764</v>
+        <v>97846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562537</v>
+        <v>562450</v>
       </c>
       <c r="R2" t="n">
-        <v>6923749</v>
+        <v>6923797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118505057</v>
+        <v>118504974</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97764</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562450</v>
+        <v>562537</v>
       </c>
       <c r="R3" t="n">
-        <v>6923797</v>
+        <v>6923749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 46548-2023 artfynd.xlsx
+++ b/artfynd/A 46548-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118505057</v>
+        <v>118504975</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562450</v>
+        <v>562401</v>
       </c>
       <c r="R2" t="n">
-        <v>6923797</v>
+        <v>6923859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504974</v>
+        <v>118505057</v>
       </c>
       <c r="B3" t="n">
-        <v>97764</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562537</v>
+        <v>562450</v>
       </c>
       <c r="R3" t="n">
-        <v>6923749</v>
+        <v>6923797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
         <v>118504966</v>
       </c>
       <c r="B4" t="n">
-        <v>97867</v>
+        <v>97874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504975</v>
+        <v>118504944</v>
       </c>
       <c r="B5" t="n">
-        <v>97764</v>
+        <v>91443</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,34 +1001,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562401</v>
+        <v>562381</v>
       </c>
       <c r="R5" t="n">
-        <v>6923859</v>
+        <v>6923819</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504944</v>
+        <v>118504974</v>
       </c>
       <c r="B6" t="n">
-        <v>91436</v>
+        <v>97771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,38 +1107,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>223591</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562381</v>
+        <v>562537</v>
       </c>
       <c r="R6" t="n">
-        <v>6923819</v>
+        <v>6923749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 46548-2023 artfynd.xlsx
+++ b/artfynd/A 46548-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504975</v>
+        <v>118504966</v>
       </c>
       <c r="B2" t="n">
-        <v>97771</v>
+        <v>97874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562401</v>
+        <v>562527</v>
       </c>
       <c r="R2" t="n">
-        <v>6923859</v>
+        <v>6923740</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118505057</v>
+        <v>118504975</v>
       </c>
       <c r="B3" t="n">
-        <v>97853</v>
+        <v>97771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562450</v>
+        <v>562401</v>
       </c>
       <c r="R3" t="n">
-        <v>6923797</v>
+        <v>6923859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118504966</v>
+        <v>118505057</v>
       </c>
       <c r="B4" t="n">
-        <v>97874</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562527</v>
+        <v>562450</v>
       </c>
       <c r="R4" t="n">
-        <v>6923740</v>
+        <v>6923797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504944</v>
+        <v>118504974</v>
       </c>
       <c r="B5" t="n">
-        <v>91443</v>
+        <v>97771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,38 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562381</v>
+        <v>562537</v>
       </c>
       <c r="R5" t="n">
-        <v>6923819</v>
+        <v>6923749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504974</v>
+        <v>118504944</v>
       </c>
       <c r="B6" t="n">
-        <v>97771</v>
+        <v>91443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,34 +1103,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562537</v>
+        <v>562381</v>
       </c>
       <c r="R6" t="n">
-        <v>6923749</v>
+        <v>6923819</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 46548-2023 artfynd.xlsx
+++ b/artfynd/A 46548-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504979</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504944</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504943</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505056</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505057</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504966</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504935</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504974</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,8 +1602,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504975</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>